--- a/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/26.03.25 - Лаба №4/Дима/lab4.xlsx
+++ b/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/26.03.25 - Лаба №4/Дима/lab4.xlsx
@@ -5,20 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luvidmi\Desktop\git\Codespace\Файлы\1 курс\2 семестр\Теоретическая информатика\Лабы\26.03.25 - Лаба №4\Дима\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luvidmi\Desktop\gitRep\Codespace\Файлы\1 курс\2 семестр\Теоретическая информатика\Лабы\26.03.25 - Лаба №4\Дима\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB9CADB-4655-4221-AE74-C15FAB381F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E0346A-59BF-412B-ABCA-36BAA1D2CC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="5265" windowWidth="23640" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$2:$G$17</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="0">Лист1!$A$89:$G$89</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="0">Лист1!$A$85:$G$87</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="0">Лист1!$A$124:$G$124</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="0">Лист1!$A$120:$G$122</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="28">
   <si>
     <t>Ведомость учёта заказов</t>
   </si>
@@ -110,6 +132,21 @@
   </si>
   <si>
     <t>&lt;1000</t>
+  </si>
+  <si>
+    <t>&gt;=01.04.2014</t>
+  </si>
+  <si>
+    <t>&lt;=30.04.2014</t>
+  </si>
+  <si>
+    <t>&gt;</t>
+  </si>
+  <si>
+    <t>&gt;=16.05.2014</t>
+  </si>
+  <si>
+    <t>&lt;=31.05.2014</t>
   </si>
 </sst>
 </file>
@@ -241,8 +278,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -252,14 +300,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -540,1329 +580,1389 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>41775</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="2">
         <v>24</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="2">
         <v>24</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="2">
         <v>2100</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="2">
         <v>50400</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="H3" t="b">
+        <f>D3&gt;E3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3">
         <v>41783</v>
       </c>
-      <c r="D4" s="5">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="D4" s="2">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2">
         <v>3100</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="2">
         <v>37200</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="H4" t="b">
+        <f t="shared" ref="H4:H17" si="0">D4&gt;E4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>41751</v>
       </c>
-      <c r="D5" s="5">
-        <v>10</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
         <v>8</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="2">
         <v>950</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="2">
         <v>7600</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="H5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3">
         <v>41735</v>
       </c>
-      <c r="D6" s="5">
-        <v>10</v>
-      </c>
-      <c r="E6" s="5">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="D6" s="2">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2">
         <v>3100</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="2">
         <v>31000</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="H6" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="3">
         <v>41818</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="2">
         <v>8</v>
       </c>
-      <c r="E7" s="5">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="2">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2">
         <v>2100</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="2">
         <v>21000</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="H7" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="3">
         <v>41770</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="2">
         <v>15</v>
       </c>
-      <c r="E8" s="5">
-        <v>18</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="2">
+        <v>18</v>
+      </c>
+      <c r="F8" s="2">
         <v>600</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="2">
         <v>10800</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="H8" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="3">
         <v>41819</v>
       </c>
-      <c r="D9" s="5">
-        <v>10</v>
-      </c>
-      <c r="E9" s="5">
-        <v>12</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="D9" s="2">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2">
         <v>2300</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="2">
         <v>27600</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="H9" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <v>41797</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="2">
         <v>5</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="2">
         <v>5</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="2">
         <v>4200</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="2">
         <v>21000</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="H10" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="3">
         <v>41776</v>
       </c>
-      <c r="D11" s="5">
-        <v>12</v>
-      </c>
-      <c r="E11" s="5">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="D11" s="2">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2">
         <v>1200</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="2">
         <v>12000</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="H11" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>41793</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="2">
         <v>22</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="2">
         <v>20</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="2">
         <v>4200</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="2">
         <v>84000</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="H12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3">
         <v>41739</v>
       </c>
-      <c r="D13" s="5">
-        <v>18</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" s="2">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2">
         <v>16</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="2">
         <v>3100</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="2">
         <v>49600</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="H13" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="3">
         <v>41786</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="2">
         <v>16</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="2">
         <v>20</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="2">
         <v>2300</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="2">
         <v>46000</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="H14" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="3">
         <v>41762</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="2">
         <v>15</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="2">
         <v>15</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="2">
         <v>1200</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="2">
         <v>18000</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="H15" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="3">
         <v>41788</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="2">
         <v>8</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="2">
         <v>8</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="2">
         <v>900</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="2">
         <v>7200</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="H16" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="3">
         <v>41755</v>
       </c>
-      <c r="D17" s="5">
-        <v>10</v>
-      </c>
-      <c r="E17" s="5">
-        <v>10</v>
-      </c>
-      <c r="F17" s="5">
+      <c r="D17" s="2">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2">
+        <v>10</v>
+      </c>
+      <c r="F17" s="2">
         <v>600</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="2">
         <v>6000</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="H17" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="3">
         <v>41819</v>
       </c>
-      <c r="D21" s="5">
-        <v>10</v>
-      </c>
-      <c r="E21" s="5">
-        <v>12</v>
-      </c>
-      <c r="F21" s="5">
+      <c r="D21" s="2">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2">
+        <v>12</v>
+      </c>
+      <c r="F21" s="2">
         <v>2300</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="2">
         <v>27600</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="3">
         <v>41797</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="2">
         <v>5</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="2">
         <v>5</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="2">
         <v>4200</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="2">
         <v>21000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="3">
         <v>41776</v>
       </c>
-      <c r="D23" s="5">
-        <v>12</v>
-      </c>
-      <c r="E23" s="5">
-        <v>10</v>
-      </c>
-      <c r="F23" s="5">
+      <c r="D23" s="2">
+        <v>12</v>
+      </c>
+      <c r="E23" s="2">
+        <v>10</v>
+      </c>
+      <c r="F23" s="2">
         <v>1200</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="2">
         <v>12000</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="8"/>
-    </row>
-    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="24" spans="1:8" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="B27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3">
         <v>41783</v>
       </c>
-      <c r="D27" s="5">
-        <v>12</v>
-      </c>
-      <c r="E27" s="5">
-        <v>12</v>
-      </c>
-      <c r="F27" s="5">
+      <c r="D27" s="2">
+        <v>12</v>
+      </c>
+      <c r="E27" s="2">
+        <v>12</v>
+      </c>
+      <c r="F27" s="2">
         <v>3100</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="2">
         <v>37200</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="3">
         <v>41797</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="2">
         <v>5</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="2">
         <v>5</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="2">
         <v>4200</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="2">
         <v>21000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="5" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="3">
         <v>41793</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="2">
         <v>22</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="2">
         <v>20</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="2">
         <v>4200</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="2">
         <v>84000</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="8"/>
-    </row>
-    <row r="32" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+    <row r="30" spans="1:8" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="5"/>
+    </row>
+    <row r="32" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="3">
         <v>41775</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="2">
         <v>24</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="2">
         <v>24</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="2">
         <v>2100</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="2">
         <v>50400</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
+      <c r="B34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="3">
         <v>41783</v>
       </c>
-      <c r="D34" s="5">
-        <v>12</v>
-      </c>
-      <c r="E34" s="5">
-        <v>12</v>
-      </c>
-      <c r="F34" s="5">
+      <c r="D34" s="2">
+        <v>12</v>
+      </c>
+      <c r="E34" s="2">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2">
         <v>3100</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="2">
         <v>37200</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="3">
         <v>41751</v>
       </c>
-      <c r="D35" s="5">
-        <v>10</v>
-      </c>
-      <c r="E35" s="5">
+      <c r="D35" s="2">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2">
         <v>8</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="2">
         <v>950</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="2">
         <v>7600</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="3">
         <v>41819</v>
       </c>
-      <c r="D36" s="5">
-        <v>10</v>
-      </c>
-      <c r="E36" s="5">
-        <v>12</v>
-      </c>
-      <c r="F36" s="5">
+      <c r="D36" s="2">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2">
         <v>2300</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="2">
         <v>27600</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="3">
         <v>41797</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="2">
         <v>5</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="2">
         <v>5</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="2">
         <v>4200</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="2">
         <v>21000</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="3">
         <v>41776</v>
       </c>
-      <c r="D38" s="5">
-        <v>12</v>
-      </c>
-      <c r="E38" s="5">
-        <v>10</v>
-      </c>
-      <c r="F38" s="5">
+      <c r="D38" s="2">
+        <v>12</v>
+      </c>
+      <c r="E38" s="2">
+        <v>10</v>
+      </c>
+      <c r="F38" s="2">
         <v>1200</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="2">
         <v>12000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="8"/>
+    <row r="39" spans="1:7" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="5"/>
     </row>
     <row r="41" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
+      <c r="A42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="3">
         <v>41735</v>
       </c>
-      <c r="D42" s="5">
-        <v>10</v>
-      </c>
-      <c r="E42" s="5">
-        <v>10</v>
-      </c>
-      <c r="F42" s="5">
+      <c r="D42" s="2">
+        <v>10</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2">
         <v>3100</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="2">
         <v>31000</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
+      <c r="A43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3">
         <v>41739</v>
       </c>
-      <c r="D43" s="5">
-        <v>18</v>
-      </c>
-      <c r="E43" s="5">
+      <c r="D43" s="2">
+        <v>18</v>
+      </c>
+      <c r="E43" s="2">
         <v>16</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="2">
         <v>3100</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="2">
         <v>49600</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="8"/>
+    <row r="44" spans="1:7" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="5"/>
     </row>
     <row r="46" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="6">
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3">
         <v>41783</v>
       </c>
-      <c r="D47" s="5">
-        <v>12</v>
-      </c>
-      <c r="E47" s="5">
-        <v>12</v>
-      </c>
-      <c r="F47" s="5">
+      <c r="D47" s="2">
+        <v>12</v>
+      </c>
+      <c r="E47" s="2">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2">
         <v>3100</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="2">
         <v>37200</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="5" t="s">
+      <c r="A48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="3">
         <v>41770</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="2">
         <v>15</v>
       </c>
-      <c r="E48" s="5">
-        <v>18</v>
-      </c>
-      <c r="F48" s="5">
+      <c r="E48" s="2">
+        <v>18</v>
+      </c>
+      <c r="F48" s="2">
         <v>600</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="2">
         <v>10800</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="3">
         <v>41776</v>
       </c>
-      <c r="D49" s="5">
-        <v>12</v>
-      </c>
-      <c r="E49" s="5">
-        <v>10</v>
-      </c>
-      <c r="F49" s="5">
+      <c r="D49" s="2">
+        <v>12</v>
+      </c>
+      <c r="E49" s="2">
+        <v>10</v>
+      </c>
+      <c r="F49" s="2">
         <v>1200</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="2">
         <v>12000</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="A50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="3">
         <v>41786</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="2">
         <v>16</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="2">
         <v>20</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="2">
         <v>2300</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="2">
         <v>46000</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="A51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="3">
         <v>41762</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="2">
         <v>15</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="2">
         <v>15</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="2">
         <v>1200</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="2">
         <v>18000</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="8"/>
+    <row r="52" spans="1:7" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="5"/>
     </row>
     <row r="54" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B55" s="5" t="s">
+      <c r="A55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="3">
         <v>41793</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="2">
         <v>22</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="2">
         <v>20</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="2">
         <v>4200</v>
       </c>
-      <c r="G55" s="5">
+      <c r="G55" s="2">
         <v>84000</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="8"/>
+    <row r="56" spans="1:7" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="5"/>
     </row>
     <row r="58" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="3">
         <v>41775</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="2">
         <v>24</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="2">
         <v>24</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="2">
         <v>2100</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="2">
         <v>50400</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="A60" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="3">
         <v>41793</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="2">
         <v>22</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="2">
         <v>20</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="2">
         <v>4200</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="2">
         <v>84000</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="6">
+      <c r="A61" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="3">
         <v>41739</v>
       </c>
-      <c r="D61" s="5">
-        <v>18</v>
-      </c>
-      <c r="E61" s="5">
+      <c r="D61" s="2">
+        <v>18</v>
+      </c>
+      <c r="E61" s="2">
         <v>16</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="2">
         <v>3100</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="2">
         <v>49600</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="A62" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="3">
         <v>41786</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="2">
         <v>16</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="2">
         <v>20</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="2">
         <v>2300</v>
       </c>
-      <c r="G62" s="5">
+      <c r="G62" s="2">
         <v>46000</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="8"/>
+    <row r="63" spans="1:7" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="5"/>
     </row>
     <row r="65" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="6">
+      <c r="B66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="3">
         <v>41783</v>
       </c>
-      <c r="D66" s="5">
-        <v>12</v>
-      </c>
-      <c r="E66" s="5">
-        <v>12</v>
-      </c>
-      <c r="F66" s="5">
+      <c r="D66" s="2">
+        <v>12</v>
+      </c>
+      <c r="E66" s="2">
+        <v>12</v>
+      </c>
+      <c r="F66" s="2">
         <v>3100</v>
       </c>
-      <c r="G66" s="5">
+      <c r="G66" s="2">
         <v>37200</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="6">
+      <c r="A67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="3">
         <v>41735</v>
       </c>
-      <c r="D67" s="5">
-        <v>10</v>
-      </c>
-      <c r="E67" s="5">
-        <v>10</v>
-      </c>
-      <c r="F67" s="5">
+      <c r="D67" s="2">
+        <v>10</v>
+      </c>
+      <c r="E67" s="2">
+        <v>10</v>
+      </c>
+      <c r="F67" s="2">
         <v>3100</v>
       </c>
-      <c r="G67" s="5">
+      <c r="G67" s="2">
         <v>31000</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="3">
         <v>41819</v>
       </c>
-      <c r="D68" s="5">
-        <v>10</v>
-      </c>
-      <c r="E68" s="5">
-        <v>12</v>
-      </c>
-      <c r="F68" s="5">
+      <c r="D68" s="2">
+        <v>10</v>
+      </c>
+      <c r="E68" s="2">
+        <v>12</v>
+      </c>
+      <c r="F68" s="2">
         <v>2300</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G68" s="2">
         <v>27600</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="3">
         <v>41797</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="2">
         <v>5</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="2">
         <v>5</v>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="2">
         <v>4200</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G69" s="2">
         <v>21000</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B70" s="5" t="s">
+      <c r="A70" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="3">
         <v>41793</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="2">
         <v>22</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="2">
         <v>20</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="2">
         <v>4200</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G70" s="2">
         <v>84000</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="6">
+      <c r="A71" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="3">
         <v>41739</v>
       </c>
-      <c r="D71" s="5">
-        <v>18</v>
-      </c>
-      <c r="E71" s="5">
+      <c r="D71" s="2">
+        <v>18</v>
+      </c>
+      <c r="E71" s="2">
         <v>16</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="2">
         <v>3100</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="2">
         <v>49600</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="A72" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="3">
         <v>41786</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="2">
         <v>16</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="2">
         <v>20</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="2">
         <v>2300</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="2">
         <v>46000</v>
       </c>
     </row>
-    <row r="73" spans="1:7" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:7" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="1:7" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:7" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E76" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F76" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1876,117 +1976,117 @@
       </c>
     </row>
     <row r="79" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E79" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F79" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B80" s="5" t="s">
+      <c r="A80" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="3">
         <v>41793</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="2">
         <v>22</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="2">
         <v>20</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="2">
         <v>4200</v>
       </c>
-      <c r="G80" s="5">
+      <c r="G80" s="2">
         <v>84000</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="6">
+      <c r="A81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="3">
         <v>41739</v>
       </c>
-      <c r="D81" s="5">
-        <v>18</v>
-      </c>
-      <c r="E81" s="5">
+      <c r="D81" s="2">
+        <v>18</v>
+      </c>
+      <c r="E81" s="2">
         <v>16</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="2">
         <v>3100</v>
       </c>
-      <c r="G81" s="5">
+      <c r="G81" s="2">
         <v>49600</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B82" s="5" t="s">
+      <c r="A82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="3">
         <v>41786</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="2">
         <v>16</v>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="2">
         <v>20</v>
       </c>
-      <c r="F82" s="5">
+      <c r="F82" s="2">
         <v>2300</v>
       </c>
-      <c r="G82" s="5">
+      <c r="G82" s="2">
         <v>46000</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E85" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2001,233 +2101,709 @@
       </c>
     </row>
     <row r="89" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="E89" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F89" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
+      <c r="A90" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="3">
         <v>41775</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="2">
         <v>24</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E90" s="2">
         <v>24</v>
       </c>
-      <c r="F90" s="5">
+      <c r="F90" s="2">
         <v>2100</v>
       </c>
-      <c r="G90" s="5">
+      <c r="G90" s="2">
         <v>50400</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
+      <c r="A91" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="3">
         <v>41751</v>
       </c>
-      <c r="D91" s="5">
-        <v>10</v>
-      </c>
-      <c r="E91" s="5">
+      <c r="D91" s="2">
+        <v>10</v>
+      </c>
+      <c r="E91" s="2">
         <v>8</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="2">
         <v>950</v>
       </c>
-      <c r="G91" s="5">
+      <c r="G91" s="2">
         <v>7600</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B92" s="5" t="s">
+      <c r="A92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="3">
         <v>41770</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D92" s="2">
         <v>15</v>
       </c>
-      <c r="E92" s="5">
-        <v>18</v>
-      </c>
-      <c r="F92" s="5">
+      <c r="E92" s="2">
+        <v>18</v>
+      </c>
+      <c r="F92" s="2">
         <v>600</v>
       </c>
-      <c r="G92" s="5">
+      <c r="G92" s="2">
         <v>10800</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B93" s="5" t="s">
+      <c r="A93" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="3">
         <v>41793</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D93" s="2">
         <v>22</v>
       </c>
-      <c r="E93" s="5">
+      <c r="E93" s="2">
         <v>20</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="2">
         <v>4200</v>
       </c>
-      <c r="G93" s="5">
+      <c r="G93" s="2">
         <v>84000</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="6">
+      <c r="A94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="3">
         <v>41739</v>
       </c>
-      <c r="D94" s="5">
-        <v>18</v>
-      </c>
-      <c r="E94" s="5">
+      <c r="D94" s="2">
+        <v>18</v>
+      </c>
+      <c r="E94" s="2">
         <v>16</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="2">
         <v>3100</v>
       </c>
-      <c r="G94" s="5">
+      <c r="G94" s="2">
         <v>49600</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B95" s="5" t="s">
+      <c r="A95" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="3">
         <v>41786</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="2">
         <v>16</v>
       </c>
-      <c r="E95" s="5">
+      <c r="E95" s="2">
         <v>20</v>
       </c>
-      <c r="F95" s="5">
+      <c r="F95" s="2">
         <v>2300</v>
       </c>
-      <c r="G95" s="5">
+      <c r="G95" s="2">
         <v>46000</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B96" s="5" t="s">
+      <c r="A96" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="3">
         <v>41788</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D96" s="2">
         <v>8</v>
       </c>
-      <c r="E96" s="5">
+      <c r="E96" s="2">
         <v>8</v>
       </c>
-      <c r="F96" s="5">
+      <c r="F96" s="2">
         <v>900</v>
       </c>
-      <c r="G96" s="5">
+      <c r="G96" s="2">
         <v>7200</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B97" s="5" t="s">
+      <c r="A97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="3">
         <v>41755</v>
       </c>
-      <c r="D97" s="5">
-        <v>10</v>
-      </c>
-      <c r="E97" s="5">
-        <v>10</v>
-      </c>
-      <c r="F97" s="5">
+      <c r="D97" s="2">
+        <v>10</v>
+      </c>
+      <c r="E97" s="2">
+        <v>10</v>
+      </c>
+      <c r="F97" s="2">
         <v>600</v>
       </c>
-      <c r="G97" s="5">
+      <c r="G97" s="2">
         <v>6000</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="4" t="s">
+      <c r="E100" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B101" t="str">
+        <f>"Пароварка"</f>
+        <v>Пароварка</v>
+      </c>
+      <c r="C101" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="3">
+        <v>41735</v>
+      </c>
+      <c r="D105" s="2">
+        <v>10</v>
+      </c>
+      <c r="E105" s="2">
+        <v>10</v>
+      </c>
+      <c r="F105" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G105" s="2">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="3">
+        <v>41739</v>
+      </c>
+      <c r="D106" s="2">
+        <v>18</v>
+      </c>
+      <c r="E106" s="2">
+        <v>16</v>
+      </c>
+      <c r="F106" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G106" s="2">
+        <v>49600</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+    </row>
+    <row r="109" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="9"/>
+      <c r="B110" s="9"/>
+      <c r="D110" t="s">
+        <v>25</v>
+      </c>
+      <c r="E110">
+        <f>E3</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="str" cm="1">
+        <f t="array" ref="A114:G117">_xlfn._xlws.FILTER(A3:G17, H3:H17=TRUE)</f>
+        <v>Белых А. П.</v>
+      </c>
+      <c r="B114" s="2" t="str">
+        <v>Тостер</v>
+      </c>
+      <c r="C114" s="2">
+        <v>41751</v>
+      </c>
+      <c r="D114" s="2">
+        <v>10</v>
+      </c>
+      <c r="E114" s="2">
+        <v>8</v>
+      </c>
+      <c r="F114" s="2">
+        <v>950</v>
+      </c>
+      <c r="G114" s="2">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="str">
+        <v>Михайлов Н. А.</v>
+      </c>
+      <c r="B115" s="2" t="str">
+        <v>Кофеварка</v>
+      </c>
+      <c r="C115" s="2">
+        <v>41776</v>
+      </c>
+      <c r="D115" s="2">
+        <v>12</v>
+      </c>
+      <c r="E115" s="2">
+        <v>10</v>
+      </c>
+      <c r="F115" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G115" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="str">
+        <v>Седова Н. Р.</v>
+      </c>
+      <c r="B116" s="2" t="str">
+        <v>Мультиварка</v>
+      </c>
+      <c r="C116" s="2">
+        <v>41793</v>
+      </c>
+      <c r="D116" s="2">
+        <v>22</v>
+      </c>
+      <c r="E116" s="2">
+        <v>20</v>
+      </c>
+      <c r="F116" s="2">
+        <v>4200</v>
+      </c>
+      <c r="G116" s="2">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="str">
+        <v>Седова Н. Р.</v>
+      </c>
+      <c r="B117" s="2" t="str">
+        <v>Пароварка</v>
+      </c>
+      <c r="C117" s="2">
+        <v>41739</v>
+      </c>
+      <c r="D117" s="2">
+        <v>18</v>
+      </c>
+      <c r="E117" s="2">
+        <v>16</v>
+      </c>
+      <c r="F117" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G117" s="2">
+        <v>49600</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="9"/>
+      <c r="B121" s="9"/>
+      <c r="C121" t="s">
+        <v>26</v>
+      </c>
+      <c r="D121" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C122" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="3">
+        <v>41775</v>
+      </c>
+      <c r="D125" s="2">
+        <v>24</v>
+      </c>
+      <c r="E125" s="2">
+        <v>24</v>
+      </c>
+      <c r="F125" s="2">
+        <v>2100</v>
+      </c>
+      <c r="G125" s="2">
+        <v>50400</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" s="3">
+        <v>41783</v>
+      </c>
+      <c r="D126" s="2">
+        <v>12</v>
+      </c>
+      <c r="E126" s="2">
+        <v>12</v>
+      </c>
+      <c r="F126" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G126" s="2">
+        <v>37200</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" s="3">
+        <v>41776</v>
+      </c>
+      <c r="D127" s="2">
+        <v>12</v>
+      </c>
+      <c r="E127" s="2">
+        <v>10</v>
+      </c>
+      <c r="F127" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G127" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" s="3">
+        <v>41739</v>
+      </c>
+      <c r="D128" s="2">
+        <v>18</v>
+      </c>
+      <c r="E128" s="2">
+        <v>16</v>
+      </c>
+      <c r="F128" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G128" s="2">
+        <v>49600</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" s="3">
+        <v>41786</v>
+      </c>
+      <c r="D129" s="2">
+        <v>16</v>
+      </c>
+      <c r="E129" s="2">
+        <v>20</v>
+      </c>
+      <c r="F129" s="2">
+        <v>2300</v>
+      </c>
+      <c r="G129" s="2">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130" s="3">
+        <v>41788</v>
+      </c>
+      <c r="D130" s="2">
+        <v>8</v>
+      </c>
+      <c r="E130" s="2">
+        <v>8</v>
+      </c>
+      <c r="F130" s="2">
+        <v>900</v>
+      </c>
+      <c r="G130" s="2">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" s="3">
+        <v>41793</v>
+      </c>
+      <c r="D131" s="2">
+        <v>22</v>
+      </c>
+      <c r="E131" s="2">
+        <v>20</v>
+      </c>
+      <c r="F131" s="2">
+        <v>4200</v>
+      </c>
+      <c r="G131" s="2">
+        <v>84000</v>
       </c>
     </row>
   </sheetData>
